--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Louise marche avec maman. Elles vont au marché. Les fruits brillent. La marchande sourit. Louise dit : bonjour. Maman dit : bonjour. Louise pointe une poire. Elle dit : s'il te plaît. La marchande tend la poire. Louise dit : merci. Maman dit : merci. Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.</t>
+          <t>Louise marche avec maman. Elles vont au marché. Les fruits brillent. La marchande sourit. Bonjour. Bonjour. Louise pointe une poire. S'il te plaît. La marchande tend la poire. Merci. Merci. Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Louise marche avec maman. Elles vont au marché. Les fruits brillent. La marchande sourit.
+enfant-f|Bonjour.
+maman|Bonjour.
+narrateur|Louise pointe une poire.
+narrateur|S'il te plaît.
+narrateur|La marchande tend la poire.
+enfant-f|Merci.
+maman|Merci.
+narrateur|Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Louise veut la poire. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Louise a dit bonjour. Elle a dit s'il te plaît. Elle a dit merci. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Louise croque un bout de poire. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Louise veut la poire. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Louise a dit bonjour. Elle a dit s'il te plaît. Elle a dit merci. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Louise croque un bout de poire. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Louise dit bonjour au marché</t>
+          <t>La poire de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut une poire au marché. Avec maman, elle dit bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Louise marche avec maman. Elles vont au marché. Les fruits brillent. La marchande sourit. Bonjour. Bonjour. Louise pointe une poire. S'il te plaît. La marchande tend la poire. Merci. Merci. Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.</t>
+          <t>Une feuille jaune colle au bois de l'étal. Le vent la soulève, puis la repose. Une balance de fer fait tic, tout doux. Les poires sont vertes, avec un côté doré. Ça sent le sucré, tout près du nez. Un torchon à carreaux couvre une caisse. Maman a un panier d'osier à la main. L'osier gratte un peu, contre son manteau. Tu entends la balance, Sarah ? Elle fait tic. Oui. Tic, tic. En ce moment, Sarah s'approche des poires. Une poire courte brille, bien ronde. Sa peau est lisse, un peu froide. Celle-là, maman. On dit bonjour d'abord. Ensuite on demande. La marchande range des feuilles dans une caisse. Sarah se tient près du panier. Bonjour. Bonjour. La marchande se tourne. Son tablier est vert, comme les poires. Une poire, s'il te plaît. Très bien, Sarah. La marchande pose la poire dans le panier. L'osier craque un tout petit peu. Merci. Bravo. Tu as dit merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle a dormi dans la caisse. Tu as dit s'il te plaît. Le vent reprend la feuille jaune. La feuille s'envole vers la rue. Tu as dit les mots, Sarah ? Bonjour. S'il te plaît. Merci. Oui. C'est du bon travail. Sarah tient une anse du panier. Le panier penche un peu, tout doux. Ils marchent le long de l'étal.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Louise marche avec maman. Elles vont au marché. Les fruits brillent. La marchande sourit.
+          <t xml:space="preserve">narrateur|Une feuille jaune colle au bois de l'étal.
+narrateur|Le vent la soulève, puis la repose.
+narrateur|Une balance de fer fait tic, tout doux.
+narrateur|Les poires sont vertes, avec un côté doré.
+narrateur|Ça sent le sucré, tout près du nez.
+narrateur|Un torchon à carreaux couvre une caisse.
+narrateur|Maman a un panier d'osier à la main.
+narrateur|L'osier gratte un peu, contre son manteau.
+maman|Tu entends la balance, Sarah ?
+enfant-f|Elle fait tic.
+maman|Oui.
+maman|Tic, tic.
+narrateur|En ce moment, Sarah s'approche des poires.
+narrateur|Une poire courte brille, bien ronde.
+narrateur|Sa peau est lisse, un peu froide.
+enfant-f|Celle-là, maman.
+maman|On dit bonjour d'abord.
+maman|Ensuite on demande.
+narrateur|La marchande range des feuilles dans une caisse.
+narrateur|Sarah se tient près du panier.
 enfant-f|Bonjour.
 maman|Bonjour.
-narrateur|Louise pointe une poire.
-narrateur|S'il te plaît.
-narrateur|La marchande tend la poire.
+narrateur|La marchande se tourne.
+narrateur|Son tablier est vert, comme les poires.
+enfant-f|Une poire, s'il te plaît.
+maman|Très bien, Sarah.
+narrateur|La marchande pose la poire dans le panier.
+narrateur|L'osier craque un tout petit peu.
 enfant-f|Merci.
-maman|Merci.
-narrateur|Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Bravo.
+maman|Tu as dit merci.
+narrateur|Sarah touche la poire du bout du doigt.
+narrateur|Elle est lisse.
+narrateur|Elle sent le sucré.
+enfant-f|Elle est froide, maman.
+maman|Oui.
+maman|Elle a dormi dans la caisse.
+maman|Tu as dit s'il te plaît.
+narrateur|Le vent reprend la feuille jaune.
+narrateur|La feuille s'envole vers la rue.
+maman|Tu as dit les mots, Sarah ?
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Oui.
+maman|C'est du bon travail.
+narrateur|Sarah tient une anse du panier.
+narrateur|Le panier penche un peu, tout doux.
+narrateur|Ils marchent le long de l'étal.
+</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Louise veut la poire. Que dit-elle ?</t>
+          <t>Sarah veut la poire. Que dit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1556,11 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Louise veut la poire. Que dit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t xml:space="preserve">narrateur|Sarah veut la poire.
+narrateur|Que dit-elle ?
+</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Louise a dit bonjour. Elle a dit s'il te plaît. Elle a dit merci. Maman est là.</t>
+          <t>La poire reste au fond du panier. Sarah la regarde encore. Elle est à toi, maintenant. Tu as demandé. S'il te plaît. Oui. Et avant ? Bonjour. Et après ? Merci. Bravo, Sarah. Tu as fait du bon travail. Le torchon à carreaux claque un peu, derrière eux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1729,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Louise a dit bonjour. Elle a dit s'il te plaît. Elle a dit merci. Maman est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t xml:space="preserve">narrateur|La poire reste au fond du panier.
+narrateur|Sarah la regarde encore.
+maman|Elle est à toi, maintenant.
+maman|Tu as demandé.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Et avant ?
+enfant-f|Bonjour.
+maman|Et après ?
+enfant-f|Merci.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Le torchon à carreaux claque un peu, derrière eux.
+</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Louise croque un bout de poire. Maman sourit.</t>
+          <t>Ils rentrent par le chemin des tilleuls. Les feuilles sèches craquent sous les pieds. À la maison, maman pose le panier. Sarah prend la poire à deux mains. Tu veux un bout ? Oui, maman. Sarah croque. Le jus est sucré, un peu froid. Merci, maman. Merci, Sarah. Tu as dit bonjour. Tu as dit s'il te plaît. Tu as dit merci. Les trois mots. Les trois mots. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1905,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Louise croque un bout de poire. Maman sourit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t xml:space="preserve">narrateur|Ils rentrent par le chemin des tilleuls.
+narrateur|Les feuilles sèches craquent sous les pieds.
+narrateur|À la maison, maman pose le panier.
+narrateur|Sarah prend la poire à deux mains.
+maman|Tu veux un bout ?
+enfant-f|Oui, maman.
+narrateur|Sarah croque.
+narrateur|Le jus est sucré, un peu froid.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.
+maman|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+maman|Tu as dit merci.
+enfant-f|Les trois mots.
+maman|Les trois mots.
+maman|Bravo.
+</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai eu une poire. J'ai dit s'il te plaît. Bravo, Sarah. C'est du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2088,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t xml:space="preserve">enfant-f|J'ai eu une poire.
+enfant-f|J'ai dit s'il te plaît.
+maman|Bravo, Sarah.
+maman|C'est du bon travail.
+narrateur|L'histoire est finie.
+</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille jaune colle au bois de l'étal. Le vent la soulève, puis la repose. Une balance de fer fait tic, tout doux. Les poires sont vertes, avec un côté doré. Ça sent le sucré, tout près du nez. Un torchon à carreaux couvre une caisse. Maman a un panier d'osier à la main. L'osier gratte un peu, contre son manteau. Tu entends la balance, Sarah ? Elle fait tic. Oui. Tic, tic. En ce moment, Sarah s'approche des poires. Une poire courte brille, bien ronde. Sa peau est lisse, un peu froide. Celle-là, maman. On dit bonjour d'abord. Ensuite on demande. La marchande range des feuilles dans une caisse. Sarah se tient près du panier. Bonjour. Bonjour. La marchande se tourne. Son tablier est vert, comme les poires. Une poire, s'il te plaît. Très bien, Sarah. La marchande pose la poire dans le panier. L'osier craque un tout petit peu. Merci. Bravo. Tu as dit merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle a dormi dans la caisse. Tu as dit s'il te plaît. Le vent reprend la feuille jaune. La feuille s'envole vers la rue. Tu as dit les mots, Sarah ? Bonjour. S'il te plaît. Merci. Oui. C'est du bon travail. Sarah tient une anse du panier. Le panier penche un peu, tout doux. Ils marchent le long de l'étal.</t>
+          <t>Une feuille jaune colle au bois de l'étal. Le vent la soulève, puis la repose. Une balance de fer fait tic, tout doux. Les poires sont vertes, avec un côté doré. Ça sent le sucré, tout près du nez. Un torchon à carreaux couvre une caisse. Maman a un panier d'osier à la main. L'osier gratte un peu, contre son manteau. Un oiseau picore sous l'étal, tout petit. Maman s'arrête, le panier contre la hanche. Tu entends la balance, Sarah ? Elle fait tic. Oui. Tic, tic. En ce moment, Sarah s'approche des poires. Une poire courte brille, bien ronde. Sa peau est lisse, un peu froide. Celle-là, maman. On dit bonjour d'abord. Ensuite on demande. La marchande range des feuilles dans une caisse. Sarah se tient près du panier. Bonjour. Bonjour. La marchande se tourne. Son tablier est vert, comme les poires. Une poire, s'il te plaît. Très bien, Sarah. La marchande pose la poire dans le panier. L'osier craque un tout petit peu. Merci. Bravo. Tu as dit merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle a dormi dans la caisse. Tu as dit s'il te plaît. Le vent reprend la feuille jaune. La feuille s'envole vers la rue. Tu as dit les mots, Sarah ? Bonjour. S'il te plaît. Merci. Oui. C'est du bon travail. Sarah tient une anse du panier. Le panier penche un peu, tout doux. Ils marchent le long de l'étal. La feuille jaune a disparu. Elle a volé, maman. Oui. Le vent l'a prise.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1332,6 +1332,8 @@
 narrateur|Un torchon à carreaux couvre une caisse.
 narrateur|Maman a un panier d'osier à la main.
 narrateur|L'osier gratte un peu, contre son manteau.
+narrateur|Un oiseau picore sous l'étal, tout petit.
+narrateur|Maman s'arrête, le panier contre la hanche.
 maman|Tu entends la balance, Sarah ?
 enfant-f|Elle fait tic.
 maman|Oui.
@@ -1373,6 +1375,10 @@
 narrateur|Sarah tient une anse du panier.
 narrateur|Le panier penche un peu, tout doux.
 narrateur|Ils marchent le long de l'étal.
+narrateur|La feuille jaune a disparu.
+enfant-f|Elle a volé, maman.
+maman|Oui.
+maman|Le vent l'a prise.
 </t>
         </is>
       </c>
@@ -2114,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2163,41 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La poire de Sarah</t>
+          <t>La poire dorée de Sarah</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COL.ECO.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -841,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah veut une poire au marché. Avec maman, elle dit bonjour, s'il te plaît, merci.</t>
+          <t>Sarah veut la poire à joue dorée dans le panier sous le poirier. Elle dit bonjour, s'il te plaît, merci. Le jus reste froid.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille jaune colle au bois de l'étal. Le vent la soulève, puis la repose. Une balance de fer fait tic, tout doux. Les poires sont vertes, avec un côté doré. Ça sent le sucré, tout près du nez. Un torchon à carreaux couvre une caisse. Maman a un panier d'osier à la main. L'osier gratte un peu, contre son manteau. Un oiseau picore sous l'étal, tout petit. Maman s'arrête, le panier contre la hanche. Tu entends la balance, Sarah ? Elle fait tic. Oui. Tic, tic. En ce moment, Sarah s'approche des poires. Une poire courte brille, bien ronde. Sa peau est lisse, un peu froide. Celle-là, maman. On dit bonjour d'abord. Ensuite on demande. La marchande range des feuilles dans une caisse. Sarah se tient près du panier. Bonjour. Bonjour. La marchande se tourne. Son tablier est vert, comme les poires. Une poire, s'il te plaît. Très bien, Sarah. La marchande pose la poire dans le panier. L'osier craque un tout petit peu. Merci. Bravo. Tu as dit merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle a dormi dans la caisse. Tu as dit s'il te plaît. Le vent reprend la feuille jaune. La feuille s'envole vers la rue. Tu as dit les mots, Sarah ? Bonjour. S'il te plaît. Merci. Oui. C'est du bon travail. Sarah tient une anse du panier. Le panier penche un peu, tout doux. Ils marchent le long de l'étal. La feuille jaune a disparu. Elle a volé, maman. Oui. Le vent l'a prise.</t>
+          <t>Les feuilles du poirier font une ombre ronde. Un panier d'osier attend au pied. Une poire a une joue dorée. Ça sent le sucré, tout près. L'herbe est chaude, un peu sèche. Un arrosoir de zinc sonne contre une pierre. Tu as vu la joue dorée, Sarah ? Elle brille, maman. C'est la poire du panier. La voisine remplit l'arrosoir. L'eau chante dans le zinc. Un oiseau picore sous l'arbre, tout petit. Il cherche une miette. Il n'en a pas. En ce moment, Sarah s'approche du panier. La poire courte est bien ronde. Sa peau est lisse, un peu froide. Celle-là, papa. On lui parle tout doux. L'arrosoir est encore plein. La voisine pose l'arrosoir près de la pierre. Elle se tourne vers le panier. Sarah se tient près de maman. Une petite feuille tient encore à la queue. Elle a un chapeau. Un tout petit chapeau. Tu demandes, Sarah.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Louise marche avec maman. Elles vont au marché. Les fruits brillent. La marchande sourit. Louise dit : &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. Maman dit : bonjour. Louise pointe une poire. Elle dit : s'il te plaît. La marchande tend la poire. Louise dit : merci. Maman dit : merci. Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les feuilles du poirier font une ombre ronde. Un panier d'osier attend au pied. Une poire a une joue dorée. Ça sent le sucré, tout près. L'herbe est chaude, un peu sèche. Un arrosoir de zinc sonne contre une pierre. Tu as vu la joue dorée, Sarah ? Elle brille, maman. C'est la poire du panier. La voisine remplit l'arrosoir. L'eau chante dans le zinc. Un oiseau picore sous l'arbre, tout petit. Il cherche une miette. Il n'en a pas. En ce moment, Sarah s'approche du panier. La poire courte est bien ronde. Sa peau est lisse, un peu froide. Celle-là, papa. On lui parle tout doux. L'arrosoir est encore plein. La voisine pose l'arrosoir près de la pierre. Elle se tourne vers le panier. Sarah se tient près de maman. Une petite feuille tient encore à la queue. Elle a un chapeau. Un tout petit chapeau. Tu demandes, Sarah.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,62 +1329,38 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrateur|Une feuille jaune colle au bois de l'étal.
-narrateur|Le vent la soulève, puis la repose.
-narrateur|Une balance de fer fait tic, tout doux.
-narrateur|Les poires sont vertes, avec un côté doré.
-narrateur|Ça sent le sucré, tout près du nez.
-narrateur|Un torchon à carreaux couvre une caisse.
-narrateur|Maman a un panier d'osier à la main.
-narrateur|L'osier gratte un peu, contre son manteau.
-narrateur|Un oiseau picore sous l'étal, tout petit.
-narrateur|Maman s'arrête, le panier contre la hanche.
-maman|Tu entends la balance, Sarah ?
-enfant-f|Elle fait tic.
-maman|Oui.
-maman|Tic, tic.
-narrateur|En ce moment, Sarah s'approche des poires.
-narrateur|Une poire courte brille, bien ronde.
+          <t>narrateur|Les feuilles du poirier font une ombre ronde.
+narrateur|Un panier d'osier attend au pied.
+narrateur|Une poire a une joue dorée.
+narrateur|Ça sent le sucré, tout près.
+narrateur|L'herbe est chaude, un peu sèche.
+narrateur|Un arrosoir de zinc sonne contre une pierre.
+maman|Tu as vu la joue dorée, Sarah ?
+enfant-f|Elle brille, maman.
+papa|C'est la poire du panier.
+narrateur|La voisine remplit l'arrosoir.
+narrateur|L'eau chante dans le zinc.
+narrateur|Un oiseau picore sous l'arbre, tout petit.
+papa|Il cherche une miette.
+enfant-f|Il n'en a pas.
+narrateur|En ce moment, Sarah s'approche du panier.
+narrateur|La poire courte est bien ronde.
 narrateur|Sa peau est lisse, un peu froide.
-enfant-f|Celle-là, maman.
-maman|On dit bonjour d'abord.
-maman|Ensuite on demande.
-narrateur|La marchande range des feuilles dans une caisse.
-narrateur|Sarah se tient près du panier.
-enfant-f|Bonjour.
-maman|Bonjour.
-narrateur|La marchande se tourne.
-narrateur|Son tablier est vert, comme les poires.
-enfant-f|Une poire, s'il te plaît.
-maman|Très bien, Sarah.
-narrateur|La marchande pose la poire dans le panier.
-narrateur|L'osier craque un tout petit peu.
-enfant-f|Merci.
-maman|Bravo.
-maman|Tu as dit merci.
-narrateur|Sarah touche la poire du bout du doigt.
-narrateur|Elle est lisse.
-narrateur|Elle sent le sucré.
-enfant-f|Elle est froide, maman.
-maman|Oui.
-maman|Elle a dormi dans la caisse.
-maman|Tu as dit s'il te plaît.
-narrateur|Le vent reprend la feuille jaune.
-narrateur|La feuille s'envole vers la rue.
-maman|Tu as dit les mots, Sarah ?
-enfant-f|Bonjour.
-enfant-f|S'il te plaît.
-enfant-f|Merci.
-maman|Oui.
-maman|C'est du bon travail.
-narrateur|Sarah tient une anse du panier.
-narrateur|Le panier penche un peu, tout doux.
-narrateur|Ils marchent le long de l'étal.
-narrateur|La feuille jaune a disparu.
-enfant-f|Elle a volé, maman.
-maman|Oui.
-maman|Le vent l'a prise.
-</t>
+enfant-f|Celle-là, papa.
+papa|On lui parle tout doux.
+maman|L'arrosoir est encore plein.
+narrateur|La voisine pose l'arrosoir près de la pierre.
+narrateur|Elle se tourne vers le panier.
+narrateur|Sarah se tient près de maman.
+narrateur|Une petite feuille tient encore à la queue.
+enfant-f|Elle a un chapeau.
+maman|Un tout petit chapeau.
+maman|Tu demandes, Sarah.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>feuilles,eau</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1392,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Louise veut la poire. Que dit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah veut la poire. Que dit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1441,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle dit s'il te plaît. Que dit Louise ?</t>
+          <t>Elle dit s'il te plaît. Que dit Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1562,9 +1543,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrateur|Sarah veut la poire.
-narrateur|Que dit-elle ?
-</t>
+          <t>narrateur|Sarah veut la poire.
+narrateur|Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>La poire reste au fond du panier. Sarah la regarde encore. Elle est à toi, maintenant. Tu as demandé. S'il te plaît. Oui. Et avant ? Bonjour. Et après ? Merci. Bravo, Sarah. Tu as fait du bon travail. Le torchon à carreaux claque un peu, derrière eux.</t>
+          <t>Bonjour. Bonjour. Une poire, s'il te plaît. Celle avec la joue. La voisine pose la poire. Elle est dans le panier d'osier. L'osier craque un tout petit peu. Merci. Merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle était sous les feuilles. Le chapeau est encore là. Tout petit. Sarah tient une anse du panier. Le panier penche un peu, tout doux. On rentre par l'herbe ? Oui, maman. L'oiseau n'est plus sous l'arbre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Louise a dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. Elle a dit s'il te plaît. Elle a dit merci. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Bonjour. Bonjour. Une poire, s'il te plaît. Celle avec la joue. La voisine pose la poire. Elle est dans le panier d'osier. L'osier craque un tout petit peu. Merci. Merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle était sous les feuilles. Le chapeau est encore là. Tout petit. Sarah tient une anse du panier. Le panier penche un peu, tout doux. On rentre par l'herbe ? Oui, maman. L'oiseau n'est plus sous l'arbre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1735,20 +1715,33 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrateur|La poire reste au fond du panier.
-narrateur|Sarah la regarde encore.
-maman|Elle est à toi, maintenant.
-maman|Tu as demandé.
-enfant-f|S'il te plaît.
+          <t>enfant-f|Bonjour.
+maman|Bonjour.
+enfant-f|Une poire, s'il te plaît.
+enfant-f|Celle avec la joue.
+narrateur|La voisine pose la poire.
+narrateur|Elle est dans le panier d'osier.
+narrateur|L'osier craque un tout petit peu.
+enfant-f|Merci.
+papa|Merci.
+narrateur|Sarah touche la poire du bout du doigt.
+narrateur|Elle est lisse.
+narrateur|Elle sent le sucré.
+enfant-f|Elle est froide, maman.
 maman|Oui.
-maman|Et avant ?
-enfant-f|Bonjour.
-maman|Et après ?
-enfant-f|Merci.
-maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
-narrateur|Le torchon à carreaux claque un peu, derrière eux.
-</t>
+maman|Elle était sous les feuilles.
+papa|Le chapeau est encore là.
+enfant-f|Tout petit.
+narrateur|Sarah tient une anse du panier.
+narrateur|Le panier penche un peu, tout doux.
+maman|On rentre par l'herbe ?
+enfant-f|Oui, maman.
+narrateur|L'oiseau n'est plus sous l'arbre.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>panier</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent par le chemin des tilleuls. Les feuilles sèches craquent sous les pieds. À la maison, maman pose le panier. Sarah prend la poire à deux mains. Tu veux un bout ? Oui, maman. Sarah croque. Le jus est sucré, un peu froid. Merci, maman. Merci, Sarah. Tu as dit bonjour. Tu as dit s'il te plaît. Tu as dit merci. Les trois mots. Les trois mots. Bravo.</t>
+          <t>Ils rentrent le long de l'herbe sèche. Les feuilles du poirier bougent un peu. À la maison, maman pose le panier. Sarah prend la poire à deux mains. Tu veux un bout ? Oui, papa. S'il te plaît. Sarah croque. Le jus est sucré, un peu froid. Merci, papa. Merci, Sarah. La petite feuille reste sur la table. Son chapeau. Oui. On la met près de la fenêtre. Elle brille encore. Moins qu'au jardin. L'ombre du poirier n'est plus là. Le panier d'osier est vide, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Louise croque un bout de poire. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils rentrent le long de l'herbe sèche. Les feuilles du poirier bougent un peu. À la maison, maman pose le panier. Sarah prend la poire à deux mains. Tu veux un bout ? Oui, papa. S'il te plaît. Sarah croque. Le jus est sucré, un peu froid. Merci, papa. Merci, Sarah. La petite feuille reste sur la table. Son chapeau. Oui. On la met près de la fenêtre. Elle brille encore. Moins qu'au jardin. L'ombre du poirier n'est plus là. Le panier d'osier est vide, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1911,23 +1904,30 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrateur|Ils rentrent par le chemin des tilleuls.
-narrateur|Les feuilles sèches craquent sous les pieds.
+          <t>narrateur|Ils rentrent le long de l'herbe sèche.
+narrateur|Les feuilles du poirier bougent un peu.
 narrateur|À la maison, maman pose le panier.
 narrateur|Sarah prend la poire à deux mains.
-maman|Tu veux un bout ?
-enfant-f|Oui, maman.
+papa|Tu veux un bout ?
+enfant-f|Oui, papa.
+enfant-f|S'il te plaît.
 narrateur|Sarah croque.
 narrateur|Le jus est sucré, un peu froid.
-enfant-f|Merci, maman.
+enfant-f|Merci, papa.
 maman|Merci, Sarah.
-maman|Tu as dit bonjour.
-maman|Tu as dit s'il te plaît.
-maman|Tu as dit merci.
-enfant-f|Les trois mots.
-maman|Les trois mots.
-maman|Bravo.
-</t>
+narrateur|La petite feuille reste sur la table.
+papa|Son chapeau.
+enfant-f|Oui.
+maman|On la met près de la fenêtre.
+enfant-f|Elle brille encore.
+papa|Moins qu'au jardin.
+narrateur|L'ombre du poirier n'est plus là.
+narrateur|Le panier d'osier est vide, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>croque</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai eu une poire. J'ai dit s'il te plaît. Bravo, Sarah. C'est du bon travail. L'histoire est finie.</t>
+          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,12 +2094,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t xml:space="preserve">enfant-f|J'ai eu une poire.
-enfant-f|J'ai dit s'il te plaît.
-maman|Bravo, Sarah.
-maman|C'est du bon travail.
-narrateur|L'histoire est finie.
-</t>
+          <t>narrateur|Il reste un bout, encore froid.
+narrateur|La feuille dort près de la fenêtre.
+maman|Bonne après-midi, Sarah.
+papa|Elle avait une joue dorée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2200,6 +2199,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée. L'histoire est finie.</t>
+          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée. L'histoire est finie.</t>
+          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,8 +2097,7 @@
           <t>narrateur|Il reste un bout, encore froid.
 narrateur|La feuille dort près de la fenêtre.
 maman|Bonne après-midi, Sarah.
-papa|Elle avait une joue dorée.
-narrateur|L'histoire est finie.</t>
+papa|Elle avait une joue dorée.</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2204,6 +2203,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>jardin, poirier, panier de la voisine</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Louise, maman</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-05.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La poire dorée de Sarah</t>
+          <t>La poire de Sarah</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin, poirier, panier de la voisine</t>
+          <t>marché, feuille jaune sur l'étal, vent, balance de fer, poires, torchon à carreaux, panier d'osier</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah veut la poire à joue dorée dans le panier sous le poirier. Elle dit bonjour, s'il te plaît, merci. Le jus reste froid.</t>
+          <t>Une feuille jaune tremble sur l'étal. Sur la poire, un éclat de poire brille. Sarah veut la poire maintenant. Elle tend la main trop vite, sans le mot : le doigt tape la balance. Elle refuse de foncer, dit s'il te plaît, obtient la poire. Merci vécu. Un éclat de poire reste pâle.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les feuilles du poirier font une ombre ronde. Un panier d'osier attend au pied. Une poire a une joue dorée. Ça sent le sucré, tout près. L'herbe est chaude, un peu sèche. Un arrosoir de zinc sonne contre une pierre. Tu as vu la joue dorée, Sarah ? Elle brille, maman. C'est la poire du panier. La voisine remplit l'arrosoir. L'eau chante dans le zinc. Un oiseau picore sous l'arbre, tout petit. Il cherche une miette. Il n'en a pas. En ce moment, Sarah s'approche du panier. La poire courte est bien ronde. Sa peau est lisse, un peu froide. Celle-là, papa. On lui parle tout doux. L'arrosoir est encore plein. La voisine pose l'arrosoir près de la pierre. Elle se tourne vers le panier. Sarah se tient près de maman. Une petite feuille tient encore à la queue. Elle a un chapeau. Un tout petit chapeau. Tu demandes, Sarah.</t>
+          <t>Une feuille jaune tremble sur l'étal. Le vent la soulève, puis la repose. Une balance de fer fait tic. Elle fait tic, papa. Tu l'entends, Sarah ? Des caisses s'alignent sous le vent. Tu tiens ma manche, Sarah ? Un torchon à carreaux couvre une caisse. Le torchon claque un peu au vent. Maman tient un panier d'osier. L'osier gratte contre le manteau. Il pique un peu. C'est l'osier, près du bras. Le vent pousse la feuille. Elle est jaune. Un oiseau picore sous l'étal. Ça sent le sucré, près du nez. Ça sent bon, maman. Ce sont les poires. Les poires sont vertes, un côté doré. Sur la poire, un éclat de poire brille. Il brille, papa. Tu le vois, sur la peau ? Sarah touche l'éclat de poire. La peau est lisse, un peu froide. Elle est froide. Je la veux, maintenant ! Tu restes près de nous ? Oui, maman. Le fer de la balance est froid. Il est froid, le fer. Le vent pique un peu les joues. J'ai les joues froides. On avance. En ce moment, Sarah s'approche des poires. Une poire courte attend, bien ronde. Celle-là ! Sarah tend la main trop vite. Le doigt tape la balance de fer. Oh. La poire reste sur l'étal. La balance fait tic, puis se tait. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je la prends ! La poire est sur le bois. Tu la vois, Sarah ? Les épaules de Sarah tombent un peu. Ça serre, dans son ventre. Papa se baisse à sa hauteur.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Les feuilles du poirier font une ombre ronde. Un panier d'osier attend au pied. Une poire a une joue dorée. Ça sent le sucré, tout près. L'herbe est chaude, un peu sèche. Un arrosoir de zinc sonne contre une pierre. Tu as vu la joue dorée, Sarah ? Elle brille, maman. C'est la poire du panier. La voisine remplit l'arrosoir. L'eau chante dans le zinc. Un oiseau picore sous l'arbre, tout petit. Il cherche une miette. Il n'en a pas. En ce moment, Sarah s'approche du panier. La poire courte est bien ronde. Sa peau est lisse, un peu froide. Celle-là, papa. On lui parle tout doux. L'arrosoir est encore plein. La voisine pose l'arrosoir près de la pierre. Elle se tourne vers le panier. Sarah se tient près de maman. Une petite feuille tient encore à la queue. Elle a un chapeau. Un tout petit chapeau. Tu demandes, Sarah.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une feuille jaune tremble sur l'étal. Le vent la soulève, puis la repose. Une balance de fer fait tic. Elle fait tic, papa. Tu l'entends, Sarah ? Des caisses s'alignent sous le vent. Tu tiens ma manche, Sarah ? Un torchon à carreaux couvre une caisse. Le torchon claque un peu au vent. Maman tient un panier d'osier. L'osier gratte contre le manteau. Il pique un peu. C'est l'osier, près du bras. Le vent pousse la feuille. Elle est jaune. Un oiseau picore sous l'étal. Ça sent le sucré, près du nez. Ça sent bon, maman. Ce sont les poires. Les poires sont vertes, un côté doré. Sur la poire, un &lt;emphasis level="moderate"&gt;éclat de poire&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la peau ? Sarah touche l'éclat de poire. La peau est lisse, un peu froide. Elle est froide. Je la veux, maintenant ! Tu restes près de nous ? Oui, maman. Le fer de la balance est froid. Il est froid, le fer. Le vent pique un peu les joues. J'ai les joues froides. On avance. En ce moment, Sarah s'approche des poires. Une poire courte attend, bien ronde. Celle-là ! Sarah tend la main trop vite. Le doigt tape la balance de fer. Oh. La poire reste sur l'étal. La balance fait tic, puis se tait. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je la prends ! La poire est sur le bois. Tu la vois, Sarah ? Les épaules de Sarah tombent un peu. Ça serre, dans son ventre. Papa se baisse à sa hauteur.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Louise marche avec maman. Elles vont au marché. Les fruits brillent. La marchande sourit. Louise dit : &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. Maman dit : bonjour. Louise pointe une poire. Elle dit : s'il te plaît. La marchande tend la poire. Louise dit : merci. Maman dit : merci. Louise tient la poire. Elle est lisse. Ça sent le sucré. Maman serre sa main. Louise répète : bonjour. S'il te plaît. Merci. Les trois mots sont là.&lt;/slow&gt; [pause]</t>
+          <t>Une feuille jaune tremble sur l'étal. Le vent la soulève, puis la repose. Une balance de fer fait tic. Elle fait tic, papa. Tu l'entends, Sarah ? Des caisses s'alignent sous le vent. Tu tiens ma manche, Sarah ? Un torchon à carreaux couvre une caisse. Le torchon claque un peu au vent. Maman tient un panier d'osier. L'osier gratte contre le manteau. Il pique un peu. C'est l'osier, près du bras. Le vent pousse la feuille. Elle est jaune. Un oiseau picore sous l'étal. Ça sent le sucré, près du nez. Ça sent bon, maman. Ce sont les poires. Les poires sont vertes, un côté doré. Sur la poire, un &lt;emphasis&gt;éclat de poire&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la peau ? Sarah touche l'éclat de poire. La peau est lisse, un peu froide. Elle est froide. Je la veux, maintenant ! Tu restes près de nous ? Oui, maman. Le fer de la balance est froid. Il est froid, le fer. Le vent pique un peu les joues. J'ai les joues froides. On avance. En ce moment, Sarah s'approche des poires. Une poire courte attend, bien ronde. Celle-là ! Sarah tend la main trop vite. Le doigt tape la balance de fer. Oh. La poire reste sur l'étal. La balance fait tic, puis se tait. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je la prends ! La poire est sur le bois. Tu la vois, Sarah ? Les épaules de Sarah tombent un peu. Ça serre, dans son ventre. Papa se baisse à sa hauteur. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,18 +1246,18 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>éclat de poire</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1324,43 +1324,70 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience_curieuse puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_la_poire_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les feuilles du poirier font une ombre ronde.
-narrateur|Un panier d'osier attend au pied.
-narrateur|Une poire a une joue dorée.
-narrateur|Ça sent le sucré, tout près.
-narrateur|L'herbe est chaude, un peu sèche.
-narrateur|Un arrosoir de zinc sonne contre une pierre.
-maman|Tu as vu la joue dorée, Sarah ?
-enfant-f|Elle brille, maman.
-papa|C'est la poire du panier.
-narrateur|La voisine remplit l'arrosoir.
-narrateur|L'eau chante dans le zinc.
-narrateur|Un oiseau picore sous l'arbre, tout petit.
-papa|Il cherche une miette.
-enfant-f|Il n'en a pas.
-narrateur|En ce moment, Sarah s'approche du panier.
-narrateur|La poire courte est bien ronde.
-narrateur|Sa peau est lisse, un peu froide.
-enfant-f|Celle-là, papa.
-papa|On lui parle tout doux.
-maman|L'arrosoir est encore plein.
-narrateur|La voisine pose l'arrosoir près de la pierre.
-narrateur|Elle se tourne vers le panier.
-narrateur|Sarah se tient près de maman.
-narrateur|Une petite feuille tient encore à la queue.
-enfant-f|Elle a un chapeau.
-maman|Un tout petit chapeau.
-maman|Tu demandes, Sarah.</t>
+          <t>narrateur|Une feuille jaune tremble sur l'étal.
+narrateur|Le vent la soulève, puis la repose.
+narrateur|Une balance de fer fait tic.
+enfant-f|Elle fait tic, papa.
+papa|Tu l'entends, Sarah ?
+narrateur|Des caisses s'alignent sous le vent.
+papa|Tu tiens ma manche, Sarah ?
+narrateur|Un torchon à carreaux couvre une caisse.
+narrateur|Le torchon claque un peu au vent.
+narrateur|Maman tient un panier d'osier.
+narrateur|L'osier gratte contre le manteau.
+enfant-f|Il pique un peu.
+maman|C'est l'osier, près du bras.
+papa|Le vent pousse la feuille.
+enfant-f|Elle est jaune.
+narrateur|Un oiseau picore sous l'étal.
+narrateur|Ça sent le sucré, près du nez.
+enfant-f|Ça sent bon, maman.
+maman|Ce sont les poires.
+narrateur|Les poires sont vertes, un côté doré.
+narrateur|Sur la poire, un éclat de poire brille.
+enfant-f|Il brille, papa.
+papa|Tu le vois, sur la peau ?
+narrateur|Sarah touche l'éclat de poire.
+narrateur|La peau est lisse, un peu froide.
+enfant-f|Elle est froide.
+enfant-f|Je la veux, maintenant !
+maman|Tu restes près de nous ?
+enfant-f|Oui, maman.
+papa|Le fer de la balance est froid.
+enfant-f|Il est froid, le fer.
+narrateur|Le vent pique un peu les joues.
+enfant-f|J'ai les joues froides.
+papa|On avance.
+narrateur|En ce moment, Sarah s'approche des poires.
+narrateur|Une poire courte attend, bien ronde.
+enfant-f|Celle-là !
+narrateur|Sarah tend la main trop vite.
+narrateur|Le doigt tape la balance de fer.
+enfant-f|Oh.
+narrateur|La poire reste sur l'étal.
+narrateur|La balance fait tic, puis se tait.
+narrateur|Le sourire de Sarah disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+enfant-f|Je la prends !
+maman|La poire est sur le bois.
+papa|Tu la vois, Sarah ?
+narrateur|Les épaules de Sarah tombent un peu.
+narrateur|Ça serre, dans son ventre.
+narrateur|Papa se baisse à sa hauteur.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>feuilles,eau</t>
+          <t>vent,balance</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1419,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah veut la poire. Que dit-elle ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah veut la &lt;emphasis level="moderate"&gt;poire&lt;/emphasis&gt;. Que dit-elle ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Louise veut la poire. Que dit-elle ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Sarah veut la &lt;emphasis&gt;poire&lt;/emphasis&gt;. Que dit-elle ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1460,7 +1487,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1468,10 +1495,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1486,34 +1513,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>poire</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1522,13 +1553,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1538,7 +1569,7 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_dit_s_il_te_plait; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1571,17 +1602,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bonjour. Bonjour. Une poire, s'il te plaît. Celle avec la joue. La voisine pose la poire. Elle est dans le panier d'osier. L'osier craque un tout petit peu. Merci. Merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle était sous les feuilles. Le chapeau est encore là. Tout petit. Sarah tient une anse du panier. Le panier penche un peu, tout doux. On rentre par l'herbe ? Oui, maman. L'oiseau n'est plus sous l'arbre.</t>
+          <t>Sarah avance trop vite vers l'étal. Celle-là, maintenant ! Sa voix se mélange au vent. Oh. La poire reste sur le bois. Elle refuse de foncer. Sarah referme la main. Elle écoute la balance, un instant. Tu veux venir près du bois ? Papa s'accroupit à la même hauteur. Sarah pose un pied près de l'étal. Le bois est lisse, un peu froid. Celle-là. S'il te plaît. Derrière l'étal, une main se tend. La poire glisse dans le panier. L'osier craque contre la poire. Merci, Sarah. Papa a entendu toute la phrase. Le ventre de Sarah se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Ça sent le sucré et le bois. La poire est à moi. Elle est dans le panier. Sarah pose une main sur la poire. La peau est un peu froide. La balance se tait.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Bonjour. Bonjour. Une poire, s'il te plaît. Celle avec la joue. La voisine pose la poire. Elle est dans le panier d'osier. L'osier craque un tout petit peu. Merci. Merci. Sarah touche la poire du bout du doigt. Elle est lisse. Elle sent le sucré. Elle est froide, maman. Oui. Elle était sous les feuilles. Le chapeau est encore là. Tout petit. Sarah tient une anse du panier. Le panier penche un peu, tout doux. On rentre par l'herbe ? Oui, maman. L'oiseau n'est plus sous l'arbre.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah avance trop vite vers l'étal. Celle-là, maintenant ! Sa voix se mélange au vent. Oh. La poire reste sur le bois. Elle refuse de foncer. Sarah referme la main. Elle écoute la balance, un instant. Tu veux venir près du bois ? Papa s'accroupit à la même hauteur. Sarah pose un pied près de l'étal. Le bois est lisse, un peu froid. Celle-là. &lt;emphasis level="moderate"&gt;S'il te plaît&lt;/emphasis&gt;. Derrière l'étal, une main se tend. La poire glisse dans le panier. L'osier craque contre la poire. Merci, Sarah. Papa a entendu toute la phrase. Le ventre de Sarah se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Ça sent le sucré et le bois. La poire est à moi. Elle est dans le panier. Sarah pose une main sur la poire. La peau est un peu froide. La balance se tait.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Louise a dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. Elle a dit s'il te plaît. Elle a dit merci. Maman est là.&lt;/slow&gt; [pause]</t>
+          <t>Sarah avance trop vite vers l'étal. Celle-là, maintenant ! Sa voix se mélange au vent. Oh. La poire reste sur le bois. Elle refuse de foncer. Sarah referme la main. Elle écoute la balance, un instant. Tu veux venir près du bois ? Papa s'accroupit à la même hauteur. Sarah pose un pied près de l'étal. Le bois est lisse, un peu froid. Celle-là. &lt;emphasis&gt;S'il te plaît&lt;/emphasis&gt;. Derrière l'étal, une main se tend. La poire glisse dans le panier. L'osier craque contre la poire. Merci, Sarah. Papa a entendu toute la phrase. Le ventre de Sarah se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Ça sent le sucré et le bois. La poire est à moi. Elle est dans le panier. Sarah pose une main sur la poire. La peau est un peu froide. La balance se tait. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1628,18 +1659,18 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1662,7 +1693,7 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>S'il te plaît</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
@@ -1672,20 +1703,20 @@
         <v>450</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1694,10 +1725,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1706,42 +1737,49 @@
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=relancer; emotion=soulagement_prudent; intensite=1; destinataire=enfant; sous_texte=la_balance_echoue_le_mot_ouvre; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>enfant-f|Bonjour.
-maman|Bonjour.
-enfant-f|Une poire, s'il te plaît.
-enfant-f|Celle avec la joue.
-narrateur|La voisine pose la poire.
-narrateur|Elle est dans le panier d'osier.
-narrateur|L'osier craque un tout petit peu.
-enfant-f|Merci.
-papa|Merci.
-narrateur|Sarah touche la poire du bout du doigt.
-narrateur|Elle est lisse.
-narrateur|Elle sent le sucré.
-enfant-f|Elle est froide, maman.
-maman|Oui.
-maman|Elle était sous les feuilles.
-papa|Le chapeau est encore là.
-enfant-f|Tout petit.
-narrateur|Sarah tient une anse du panier.
-narrateur|Le panier penche un peu, tout doux.
-maman|On rentre par l'herbe ?
-enfant-f|Oui, maman.
-narrateur|L'oiseau n'est plus sous l'arbre.</t>
+          <t>narrateur|Sarah avance trop vite vers l'étal.
+enfant-f|Celle-là, maintenant !
+narrateur|Sa voix se mélange au vent.
+enfant-f|Oh.
+narrateur|La poire reste sur le bois.
+narrateur|Elle refuse de foncer.
+narrateur|Sarah referme la main.
+narrateur|Elle écoute la balance, un instant.
+papa|Tu veux venir près du bois ?
+narrateur|Papa s'accroupit à la même hauteur.
+narrateur|Sarah pose un pied près de l'étal.
+narrateur|Le bois est lisse, un peu froid.
+enfant-f|Celle-là.
+enfant-f|S'il te plaît.
+narrateur|Derrière l'étal, une main se tend.
+narrateur|La poire glisse dans le panier.
+narrateur|L'osier craque contre la poire.
+papa|Merci, Sarah.
+narrateur|Papa a entendu toute la phrase.
+narrateur|Le ventre de Sarah se desserre.
+narrateur|Les épaules se relèvent un peu.
+maman|Tu as les mains au chaud ?
+enfant-f|Un peu, maman.
+narrateur|Ça sent le sucré et le bois.
+enfant-f|La poire est à moi.
+maman|Elle est dans le panier.
+narrateur|Sarah pose une main sur la poire.
+narrateur|La peau est un peu froide.
+narrateur|La balance se tait.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>panier</t>
+          <t>panier,osier</t>
         </is>
       </c>
     </row>
@@ -1768,17 +1806,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent le long de l'herbe sèche. Les feuilles du poirier bougent un peu. À la maison, maman pose le panier. Sarah prend la poire à deux mains. Tu veux un bout ? Oui, papa. S'il te plaît. Sarah croque. Le jus est sucré, un peu froid. Merci, papa. Merci, Sarah. La petite feuille reste sur la table. Son chapeau. Oui. On la met près de la fenêtre. Elle brille encore. Moins qu'au jardin. L'ombre du poirier n'est plus là. Le panier d'osier est vide, maintenant.</t>
+          <t>Sarah tire la poire trop vite. Je la mange, d'un coup ! La poire glisse dans l'osier. Elle penche vers le sol. Oh. Sarah avance les mains. Puis elle s'arrête net. Attends, je regarde. Papa attend, sans parler. Sarah observe l'étal, écoute le vent. Sur la peau, un éclat de poire luit. Là, près de la feuille. Sarah tient la poire des deux mains. La peau est lisse, un peu froide. Elle est froide, papa. Tu la portes jusqu'à la rue ? Oui, papa. On avance ? Oui, maman. Le vent reprend la feuille jaune. La feuille s'envole vers la rue. L'air froid revient sur les joues. Sarah serre la poire contre elle. Elle reste froide. On marche. La poire penche, puis se cale. Je la tiens. On avance. Sarah passe le long de l'étal. Le bois craque, un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent le long de l'herbe sèche. Les feuilles du poirier bougent un peu. À la maison, maman pose le panier. Sarah prend la poire à deux mains. Tu veux un bout ? Oui, papa. S'il te plaît. Sarah croque. Le jus est sucré, un peu froid. Merci, papa. Merci, Sarah. La petite feuille reste sur la table. Son chapeau. Oui. On la met près de la fenêtre. Elle brille encore. Moins qu'au jardin. L'ombre du poirier n'est plus là. Le panier d'osier est vide, maintenant.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah tire la poire trop vite. Je la mange, d'un coup ! La poire glisse dans l'osier. Elle penche vers le sol. Oh. Sarah avance les mains. Puis elle s'arrête net. Attends, je regarde. Papa attend, sans parler. Sarah observe l'étal, écoute le vent. Sur la peau, un &lt;emphasis level="moderate"&gt;éclat de poire&lt;/emphasis&gt; luit. Là, près de la feuille. Sarah tient la poire des deux mains. La peau est lisse, un peu froide. Elle est froide, papa. Tu la portes jusqu'à la rue ? Oui, papa. On avance ? Oui, maman. Le vent reprend la feuille jaune. La feuille s'envole vers la rue. L'air froid revient sur les joues. Sarah serre la poire contre elle. Elle reste froide. On marche. La poire penche, puis se cale. Je la tiens. On avance. Sarah passe le long de l'étal. Le bois craque, un peu.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Louise croque un bout de poire. Maman sourit.&lt;/slow&gt; [pause]</t>
+          <t>Sarah tire la poire trop vite. Je la mange, d'un coup ! La poire glisse dans l'osier. Elle penche vers le sol. Oh. Sarah avance les mains. Puis elle s'arrête net. Attends, je regarde. Papa attend, sans parler. Sarah observe l'étal, écoute le vent. Sur la peau, un &lt;emphasis&gt;éclat de poire&lt;/emphasis&gt; luit. Là, près de la feuille. Sarah tient la poire des deux mains. La peau est lisse, un peu froide. Elle est froide, papa. Tu la portes jusqu'à la rue ? Oui, papa. On avance ? Oui, maman. Le vent reprend la feuille jaune. La feuille s'envole vers la rue. L'air froid revient sur les joues. Sarah serre la poire contre elle. Elle reste froide. On marche. La poire penche, puis se cale. Je la tiens. On avance. Sarah passe le long de l'étal. Le bois craque, un peu. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1825,18 +1863,18 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1857,28 +1895,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de poire</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1887,10 +1929,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1899,35 +1941,50 @@
         <v>50</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_sans_regarder_l_eclat; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ils rentrent le long de l'herbe sèche.
-narrateur|Les feuilles du poirier bougent un peu.
-narrateur|À la maison, maman pose le panier.
-narrateur|Sarah prend la poire à deux mains.
-papa|Tu veux un bout ?
+          <t>narrateur|Sarah tire la poire trop vite.
+enfant-f|Je la mange, d'un coup !
+narrateur|La poire glisse dans l'osier.
+narrateur|Elle penche vers le sol.
+enfant-f|Oh.
+narrateur|Sarah avance les mains.
+narrateur|Puis elle s'arrête net.
+enfant-f|Attends, je regarde.
+narrateur|Papa attend, sans parler.
+narrateur|Sarah observe l'étal, écoute le vent.
+narrateur|Sur la peau, un éclat de poire luit.
+enfant-f|Là, près de la feuille.
+narrateur|Sarah tient la poire des deux mains.
+narrateur|La peau est lisse, un peu froide.
+enfant-f|Elle est froide, papa.
+papa|Tu la portes jusqu'à la rue ?
 enfant-f|Oui, papa.
-enfant-f|S'il te plaît.
-narrateur|Sarah croque.
-narrateur|Le jus est sucré, un peu froid.
-enfant-f|Merci, papa.
-maman|Merci, Sarah.
-narrateur|La petite feuille reste sur la table.
-papa|Son chapeau.
-enfant-f|Oui.
-maman|On la met près de la fenêtre.
-enfant-f|Elle brille encore.
-papa|Moins qu'au jardin.
-narrateur|L'ombre du poirier n'est plus là.
-narrateur|Le panier d'osier est vide, maintenant.</t>
+maman|On avance ?
+enfant-f|Oui, maman.
+narrateur|Le vent reprend la feuille jaune.
+narrateur|La feuille s'envole vers la rue.
+narrateur|L'air froid revient sur les joues.
+narrateur|Sarah serre la poire contre elle.
+enfant-f|Elle reste froide.
+papa|On marche.
+narrateur|La poire penche, puis se cale.
+enfant-f|Je la tiens.
+maman|On avance.
+narrateur|Sarah passe le long de l'étal.
+narrateur|Le bois craque, un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>croque</t>
+          <t>vent,panier</t>
         </is>
       </c>
     </row>
@@ -1954,17 +2011,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée.</t>
+          <t>La feuille brillait, papa. Tu la vois, comme sur l'étal ? Oui, dans le vent. Sarah pose la poire contre le manteau. On la garde au frais ? Oui, maman. L'étal sentait bon. Il est derrière nous. Une feuille jaune n'est plus là. Sarah respire, plus large. On rentre ? Oui. Les joues de Sarah se réchauffent. La poire reste froide sous la main. Un éclat de poire reste pâle.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Il reste un bout, encore froid. La feuille dort près de la fenêtre. Bonne après-midi, Sarah. Elle avait une joue dorée.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La feuille brillait, papa. Tu la vois, comme sur l'étal ? Oui, dans le vent. Sarah pose la poire contre le manteau. On la garde au frais ? Oui, maman. L'étal sentait bon. Il est derrière nous. Une feuille jaune n'est plus là. Sarah respire, plus large. On rentre ? Oui. Les joues de Sarah se réchauffent. La poire reste froide sous la main. Un &lt;emphasis level="moderate"&gt;éclat de poire&lt;/emphasis&gt; reste pâle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La feuille brillait, papa. Tu la vois, comme sur l'étal ? Oui, dans le vent. Sarah pose la poire contre le manteau. On la garde au frais ? Oui, maman. L'étal sentait bon. Il est derrière nous. Une feuille jaune n'est plus là. Sarah respire, plus large. On rentre ? Oui. Les joues de Sarah se réchauffent. La poire reste froide sous la main. Un &lt;emphasis&gt;éclat de poire&lt;/emphasis&gt; reste pâle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2011,7 +2068,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2019,10 +2076,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2031,12 +2088,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2045,17 +2102,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de poire</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2064,11 +2125,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2077,27 +2138,47 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_pale; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Il reste un bout, encore froid.
-narrateur|La feuille dort près de la fenêtre.
-maman|Bonne après-midi, Sarah.
-papa|Elle avait une joue dorée.</t>
+          <t>enfant-f|La feuille brillait, papa.
+papa|Tu la vois, comme sur l'étal ?
+enfant-f|Oui, dans le vent.
+narrateur|Sarah pose la poire contre le manteau.
+maman|On la garde au frais ?
+enfant-f|Oui, maman.
+enfant-f|L'étal sentait bon.
+maman|Il est derrière nous.
+narrateur|Une feuille jaune n'est plus là.
+narrateur|Sarah respire, plus large.
+papa|On rentre ?
+enfant-f|Oui.
+narrateur|Les joues de Sarah se réchauffent.
+narrateur|La poire reste froide sous la main.
+narrateur|Un éclat de poire reste pâle.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>vent</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2210,6 +2291,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
